--- a/backend/output_maquettes/MAQUETTE_A_AFFECTATION_GC.xlsx
+++ b/backend/output_maquettes/MAQUETTE_A_AFFECTATION_GC.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>49_6_</t>
+          <t>95_6_23</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -556,22 +556,22 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Chimie Minérale 2 (CM)</t>
+          <t>Analyse de Données (TP) - GC S4 Gr 1</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>ELAZHARI Mohammed</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>50_6_23</t>
+          <t>49_6_</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Chimie Minérale 2 (TD) - GC S4 Gr 1</t>
+          <t>Chimie Minérale 2 (CM)</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -589,14 +589,14 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>ELAZHARI Mohammed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>53_6_</t>
+          <t>50_6_23</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Chimie Organique 2 (CM)</t>
+          <t>Chimie Minérale 2 (TD) - GC S4 Gr 1</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -614,14 +614,14 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>EDDARIR Said</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>54_6_23</t>
+          <t>53_6_</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Chimie Organique 2 (TD) - GC S4 Gr 1</t>
+          <t>Chimie Organique 2 (CM)</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -639,14 +639,14 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>EDDARIR Said</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>33_6_</t>
+          <t>54_6_23</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Développement Personnel (CM)</t>
+          <t>Chimie Organique 2 (TD) - GC S4 Gr 1</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -664,14 +664,14 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>KOURAD Hanane</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>34_6_23</t>
+          <t>33_6_</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Développement Personnel (TD) - GC S4 Gr 1</t>
+          <t>Développement Personnel (CM)</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -689,14 +689,14 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>KOURAD Hanane</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>55_6_</t>
+          <t>34_6_23</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Éléments de Génie Chimique (CM)</t>
+          <t>Développement Personnel (TD) - GC S4 Gr 1</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -714,14 +714,14 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>ELABOUDI Ilham</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>56_6_23</t>
+          <t>55_6_</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Éléments de Génie Chimique (TD) - GC S4 Gr 1</t>
+          <t>Éléments de Génie Chimique (CM)</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -739,14 +739,14 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>ELABOUDI Ilham</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>31_6_</t>
+          <t>56_6_23</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>LTC2 Français (CM)</t>
+          <t>Éléments de Génie Chimique (TD) - GC S4 Gr 1</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -764,14 +764,14 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>El HASNAOUI Nadia</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>32_6_23</t>
+          <t>31_6_</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>LTC2 Français (TD) - GC S4 Gr 1</t>
+          <t>LTC2 Français (CM)</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -789,14 +789,14 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>El HASNAOUI Nadia</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>51_6_</t>
+          <t>32_6_23</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Thermodynamique Chimique et Cinétique (CM)</t>
+          <t>LTC2 Français (TD) - GC S4 Gr 1</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -814,14 +814,14 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>SAADI Latifa</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>52_6_23</t>
+          <t>51_6_</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Thermodynamique Chimique et Cinétique (TD) - GC S4 Gr 1</t>
+          <t>Thermodynamique Chimique et Cinétique (CM)</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -839,24 +839,24 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>SAADI Latifa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>17_2_</t>
+          <t>52_6_23</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>GC S4</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Algèbre 2 (CM)</t>
+          <t>Thermodynamique Chimique et Cinétique (TD) - GC S4 Gr 1</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -864,24 +864,24 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>CHOUKRI  Khalid</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>18_2_7</t>
+          <t>17_2_</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 1</t>
+          <t>Algèbre 2 (CM)</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -889,24 +889,24 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>CHOUKRI  Khalid</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>18_2_8</t>
+          <t>18_2_7</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 2</t>
+          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 1</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -921,17 +921,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>18_2_9</t>
+          <t>18_2_8</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 3</t>
+          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 2</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -946,17 +946,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>18_2_10</t>
+          <t>18_2_9</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 4</t>
+          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 3</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -971,17 +971,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>18_2_11</t>
+          <t>18_2_10</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 5</t>
+          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 4</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -996,17 +996,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>18_2_12</t>
+          <t>18_2_11</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 6</t>
+          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 5</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1021,17 +1021,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>15_2_</t>
+          <t>18_2_12</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Analyse 2 (CM)</t>
+          <t>Algèbre 2 (TD) - MSD-GC-GESE S2 Gr 6</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1039,24 +1039,24 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>ES SEBBAR  Brahim</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>16_2_7</t>
+          <t>15_2_</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 1</t>
+          <t>Analyse 2 (CM)</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1064,24 +1064,24 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>ES SEBBAR  Brahim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>16_2_8</t>
+          <t>16_2_7</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 2</t>
+          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 1</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1096,17 +1096,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>16_2_9</t>
+          <t>16_2_8</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 3</t>
+          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 2</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -1121,17 +1121,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>16_2_10</t>
+          <t>16_2_9</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 4</t>
+          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 3</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -1146,17 +1146,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>16_2_11</t>
+          <t>16_2_10</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 5</t>
+          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 4</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -1171,17 +1171,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>16_2_12</t>
+          <t>16_2_11</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 6</t>
+          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 5</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -1196,17 +1196,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>11_2_</t>
+          <t>16_2_12</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (CM)</t>
+          <t>Analyse 2 (TD) - MSD-GC-GESE S2 Gr 6</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -1214,24 +1214,24 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>OUAARAB Aziz</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>12_2_7</t>
+          <t>11_2_</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 1</t>
+          <t>Culture digitale (CM)</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -1239,24 +1239,24 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>OUAARAB Aziz</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>12_2_8</t>
+          <t>12_2_7</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 2</t>
+          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 1</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -1271,17 +1271,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>12_2_9</t>
+          <t>12_2_8</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 3</t>
+          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 2</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -1296,17 +1296,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>12_2_10</t>
+          <t>12_2_9</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 4</t>
+          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 3</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -1321,17 +1321,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>12_2_11</t>
+          <t>12_2_10</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 5</t>
+          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 4</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -1346,17 +1346,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>12_2_12</t>
+          <t>12_2_11</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 6</t>
+          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 5</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -1371,17 +1371,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>9_2_</t>
+          <t>12_2_12</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (CM)</t>
+          <t>Culture digitale (TD) - MSD-GC-GESE S2 Gr 6</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -1389,24 +1389,24 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>SADOUK  Leila</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>10_2_7</t>
+          <t>9_2_</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 1</t>
+          <t>Langue Etrangère 2 (CM)</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
@@ -1414,24 +1414,24 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>SADOUK  Leila</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>10_2_8</t>
+          <t>10_2_7</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 2</t>
+          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 1</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -1446,17 +1446,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>10_2_9</t>
+          <t>10_2_8</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 3</t>
+          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 2</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -1471,17 +1471,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>10_2_10</t>
+          <t>10_2_9</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 4</t>
+          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 3</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -1496,17 +1496,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>10_2_11</t>
+          <t>10_2_10</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 5</t>
+          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 4</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
@@ -1521,17 +1521,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>10_2_12</t>
+          <t>10_2_11</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 6</t>
+          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 5</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -1546,17 +1546,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>19_2_</t>
+          <t>10_2_12</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Mecanique du point / Optique (CM)</t>
+          <t>Langue Etrangère 2 (TD) - MSD-GC-GESE S2 Gr 6</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -1564,24 +1564,24 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>ZRIOUEL Sanae</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>20_2_7</t>
+          <t>19_2_</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 1</t>
+          <t>Mecanique du point / Optique (CM)</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>ZRIOUEL Sanae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>20_2_8</t>
+          <t>20_2_7</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 2</t>
+          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 1</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
@@ -1621,17 +1621,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>20_2_9</t>
+          <t>20_2_8</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 3</t>
+          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 2</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -1646,17 +1646,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>20_2_10</t>
+          <t>20_2_9</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 4</t>
+          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 3</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
@@ -1671,17 +1671,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>20_2_11</t>
+          <t>20_2_10</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 5</t>
+          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 4</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
@@ -1696,17 +1696,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>20_2_12</t>
+          <t>20_2_11</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 6</t>
+          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 5</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
@@ -1721,17 +1721,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>21_2_</t>
+          <t>20_2_12</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Structure de la matière (CM)</t>
+          <t>Mecanique du point / Optique (TD) - MSD-GC-GESE S2 Gr 6</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
@@ -1739,24 +1739,24 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>MANSOURI Mohammed</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>22_2_7</t>
+          <t>21_2_</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 1</t>
+          <t>Structure de la matière (CM)</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
@@ -1764,24 +1764,24 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>MANSOURI Mohammed</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>22_2_8</t>
+          <t>22_2_7</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 2</t>
+          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 1</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -1796,17 +1796,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>22_2_9</t>
+          <t>22_2_8</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 3</t>
+          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 2</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
@@ -1821,17 +1821,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>22_2_10</t>
+          <t>22_2_9</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 4</t>
+          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 3</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -1846,17 +1846,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>22_2_11</t>
+          <t>22_2_10</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 5</t>
+          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 4</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
@@ -1871,17 +1871,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>22_2_12</t>
+          <t>22_2_11</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 6</t>
+          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 5</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -1896,17 +1896,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3_2_</t>
+          <t>22_2_12</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Thermodynamique &amp; Mec. du Fluide (CM)</t>
+          <t>Structure de la matière (TD) - MSD-GC-GESE S2 Gr 6</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
@@ -1914,24 +1914,24 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>ER-RAKI Salah</t>
+          <t>------- (unknown)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>4_2_7</t>
+          <t>3_2_</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 1</t>
+          <t>Thermodynamique &amp; Mec. du Fluide (CM)</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
@@ -1939,24 +1939,24 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>------- (unknown)</t>
+          <t>ER-RAKI Salah</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>4_2_8</t>
+          <t>4_2_7</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 2</t>
+          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 1</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
@@ -1971,17 +1971,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>4_2_9</t>
+          <t>4_2_8</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 3</t>
+          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 2</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
@@ -1996,17 +1996,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>4_2_10</t>
+          <t>4_2_9</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 4</t>
+          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 3</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
@@ -2021,17 +2021,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4_2_11</t>
+          <t>4_2_10</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>GC S2</t>
+          <t>MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 5</t>
+          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 4</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
@@ -2046,23 +2046,48 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
+          <t>4_2_11</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 5</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>------- (unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
           <t>4_2_12</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>GC S2</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Thermodynamique &amp; Mec. du Fluide (TD) - MSD-GC-GESE S2 Gr 6</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="D68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>------- (unknown)</t>
         </is>
